--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb89fd46581f04bb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R15674e5fa64547ab"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R15674e5fa64547ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e5a8bf5ac184ea8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e5a8bf5ac184ea8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b9a1fec28cf4e9e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b9a1fec28cf4e9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8fbf4b2c4ebc4a38"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8fbf4b2c4ebc4a38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d45bc2cf5124a2d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d45bc2cf5124a2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63005603dded4f90"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63005603dded4f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra6caa629deea4303"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra6caa629deea4303"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R85342f1c49f444c1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R85342f1c49f444c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb51a5698283447e4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb51a5698283447e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8bf696209dd941f4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8bf696209dd941f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3695833fa6b45ee"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3695833fa6b45ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc7d6b28279be4480"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc7d6b28279be4480"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R121aeab6dfea4e62"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R121aeab6dfea4e62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7d4114ef2f7942b4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SparseRowAndColumnJumps/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7d4114ef2f7942b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8b500258544844d2"/>
   </x:sheets>
 </x:workbook>
 </file>
